--- a/artfynd/A 3358-2022 artfynd.xlsx
+++ b/artfynd/A 3358-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,6 +2031,342 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110941059</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550562</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7260648</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110941058</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7260628</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110941057</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550524</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7260622</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3358-2022 artfynd.xlsx
+++ b/artfynd/A 3358-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3358-2022 artfynd.xlsx
+++ b/artfynd/A 3358-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110940979</v>
+        <v>110941066</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550497.3553107829</v>
+        <v>550560</v>
       </c>
       <c r="R2" t="n">
-        <v>7260601.972373855</v>
+        <v>7260655</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110940969</v>
+        <v>110940963</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550554.1906405371</v>
+        <v>550560</v>
       </c>
       <c r="R3" t="n">
-        <v>7260685.708685622</v>
+        <v>7260652</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110941126</v>
+        <v>110941056</v>
       </c>
       <c r="B4" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550596.8186904594</v>
+        <v>550516</v>
       </c>
       <c r="R4" t="n">
-        <v>7260724.288240556</v>
+        <v>7260583</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110941058</v>
+        <v>110941057</v>
       </c>
       <c r="B5" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550539</v>
+        <v>550524</v>
       </c>
       <c r="R5" t="n">
-        <v>7260629</v>
+        <v>7260621</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110940963</v>
+        <v>110941058</v>
       </c>
       <c r="B6" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550559.7756107027</v>
+        <v>550539</v>
       </c>
       <c r="R6" t="n">
-        <v>7260651.706842074</v>
+        <v>7260629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110941123</v>
+        <v>110941059</v>
       </c>
       <c r="B7" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222741</v>
+        <v>2082</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550524.0774903947</v>
+        <v>550562</v>
       </c>
       <c r="R7" t="n">
-        <v>7260621.563788798</v>
+        <v>7260648</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110941059</v>
+        <v>110941109</v>
       </c>
       <c r="B8" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2082</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550562</v>
+        <v>550557</v>
       </c>
       <c r="R8" t="n">
-        <v>7260648</v>
+        <v>7260691</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,50 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110941057</v>
+        <v>110940969</v>
       </c>
       <c r="B9" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2082</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550524</v>
+        <v>550554</v>
       </c>
       <c r="R9" t="n">
-        <v>7260621</v>
+        <v>7260686</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110941066</v>
+        <v>110940979</v>
       </c>
       <c r="B10" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,34 +1547,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550559.717985207</v>
+        <v>550497</v>
       </c>
       <c r="R10" t="n">
-        <v>7260655.0325549</v>
+        <v>7260602</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,37 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110941109</v>
+        <v>110941123</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550557.0175549345</v>
+        <v>550524</v>
       </c>
       <c r="R11" t="n">
-        <v>7260690.747672281</v>
+        <v>7260621</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,15 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110941125</v>
+        <v>110941124</v>
       </c>
       <c r="B12" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550559.8620490439</v>
+        <v>550539</v>
       </c>
       <c r="R12" t="n">
-        <v>7260646.718265736</v>
+        <v>7260629</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,15 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110941124</v>
+        <v>110941125</v>
       </c>
       <c r="B13" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550538.9455492662</v>
+        <v>550560</v>
       </c>
       <c r="R13" t="n">
-        <v>7260628.474749288</v>
+        <v>7260647</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,6 +1970,113 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110941126</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550597</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7260724</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
